--- a/issuesNRISS/ig/ValueSet-fr-valueset-reference-externe.xlsx
+++ b/issuesNRISS/ig/ValueSet-fr-valueset-reference-externe.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T08:17:10+00:00</t>
+    <t>2026-06-18T14:12:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
